--- a/V5.0_双人执行工作区/A_数据平台/03_Smartbi证据/A03/SMARTBI_TYPE_AUDIT_V50.xlsx
+++ b/V5.0_双人执行工作区/A_数据平台/03_Smartbi证据/A03/SMARTBI_TYPE_AUDIT_V50.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="类型审计" sheetId="1" r:id="R228f6b0f81fc4049"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="类型审计" sheetId="1" r:id="Re81defe48f0a4131"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2155,7 +2155,7 @@
         <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；文本类型一致；合同来源：数据字典_V4.1.xlsx</x:v>
       </x:c>
     </x:row>
-    <x:row r="96">
+    <x:row r="96" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A96" t="str">
         <x:v>country_monthly_risk.xlsx</x:v>
       </x:c>
@@ -2169,13 +2169,13 @@
         <x:v>字符串</x:v>
       </x:c>
       <x:c r="E96" s="1" t="str">
-        <x:v>FAIL</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="F96" s="1" t="str">
-        <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同布尔，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="97">
+        <x:v>2026-09-04回写既有平台限制放行：平台无布尔型，保留true/false字符串，不转1/0。依据A03_EXECUTION_LOG_V50.txt及字段类型截图/A03_平台无布尔类型_20260826.png。PASS为例外放行，并非XML改型；原记录和证据哈希见A03_RECHECK_20260904/A03_TYPE_WAIVER_CHANGELOG_20260904.json。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A97" t="str">
         <x:v>country_monthly_risk.xlsx</x:v>
       </x:c>
@@ -2189,10 +2189,10 @@
         <x:v>字符串</x:v>
       </x:c>
       <x:c r="E97" s="1" t="str">
-        <x:v>FAIL</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="F97" s="1" t="str">
-        <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同布尔，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
+        <x:v>2026-09-04回写既有平台限制放行：平台无布尔型，保留true/false字符串，不转1/0。依据A03_EXECUTION_LOG_V50.txt及字段类型截图/A03_平台无布尔类型_20260826.png。PASS为例外放行，并非XML改型；原记录和证据哈希见A03_RECHECK_20260904/A03_TYPE_WAIVER_CHANGELOG_20260904.json。</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
@@ -2955,7 +2955,7 @@
         <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；日期类型一致；合同来源：数据字典_V4.1.xlsx</x:v>
       </x:c>
     </x:row>
-    <x:row r="136">
+    <x:row r="136" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A136" t="str">
         <x:v>country_event.xlsx</x:v>
       </x:c>
@@ -2969,10 +2969,10 @@
         <x:v>字符串</x:v>
       </x:c>
       <x:c r="E136" s="1" t="str">
-        <x:v>FAIL</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="F136" s="1" t="str">
-        <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同布尔，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
+        <x:v>2026-09-04回写既有平台限制放行：平台无布尔型，保留true/false字符串，不转1/0。依据A03_EXECUTION_LOG_V50.txt及字段类型截图/A03_平台无布尔类型_20260826.png。PASS为例外放行，并非XML改型；原记录和证据哈希见A03_RECHECK_20260904/A03_TYPE_WAIVER_CHANGELOG_20260904.json。</x:v>
       </x:c>
     </x:row>
     <x:row r="137">
@@ -3815,7 +3815,7 @@
         <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；日期类型一致；合同来源：数据字典_V4.1.xlsx</x:v>
       </x:c>
     </x:row>
-    <x:row r="179">
+    <x:row r="179" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A179" t="str">
         <x:v>global_cycle_month.xlsx</x:v>
       </x:c>
@@ -3829,10 +3829,10 @@
         <x:v>字符串</x:v>
       </x:c>
       <x:c r="E179" s="1" t="str">
-        <x:v>FAIL</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="F179" s="1" t="str">
-        <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同布尔，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
+        <x:v>2026-09-04回写既有平台限制放行：平台无布尔型，保留true/false字符串，不转1/0。依据A03_EXECUTION_LOG_V50.txt及字段类型截图/A03_平台无布尔类型_20260826.png。PASS为例外放行，并非XML改型；原记录和证据哈希见A03_RECHECK_20260904/A03_TYPE_WAIVER_CHANGELOG_20260904.json。</x:v>
       </x:c>
     </x:row>
     <x:row r="180">

--- a/V5.0_双人执行工作区/A_数据平台/03_Smartbi证据/A03/SMARTBI_TYPE_AUDIT_V50.xlsx
+++ b/V5.0_双人执行工作区/A_数据平台/03_Smartbi证据/A03/SMARTBI_TYPE_AUDIT_V50.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="类型审计" sheetId="1" r:id="Re81defe48f0a4131"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="类型审计" sheetId="1" r:id="R7f0782d12e9d400a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1995,7 +1995,7 @@
         <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；数值类型一致；合同来源：数据字典_V4.1.xlsx</x:v>
       </x:c>
     </x:row>
-    <x:row r="88">
+    <x:row r="88" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A88" t="str">
         <x:v>country_monthly_risk.xlsx</x:v>
       </x:c>
@@ -2012,7 +2012,7 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F88" s="1" t="str">
-        <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同数值，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型BIGDECIMAL；在线长浮点型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
@@ -3295,7 +3295,7 @@
         <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；数值类型一致；合同来源：数据字典_V4.1.xlsx</x:v>
       </x:c>
     </x:row>
-    <x:row r="153">
+    <x:row r="153" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A153" t="str">
         <x:v>global_cycle_month.xlsx</x:v>
       </x:c>
@@ -3312,10 +3312,10 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F153" s="1" t="str">
-        <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同数值，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="154">
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型DOUBLE；在线浮点型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A154" t="str">
         <x:v>global_cycle_month.xlsx</x:v>
       </x:c>
@@ -3332,7 +3332,7 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F154" s="1" t="str">
-        <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同数值，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型DOUBLE；在线浮点型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
       </x:c>
     </x:row>
     <x:row r="155">
@@ -3375,7 +3375,7 @@
         <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；数值类型一致；合同来源：数据字典_V4.1.xlsx</x:v>
       </x:c>
     </x:row>
-    <x:row r="157">
+    <x:row r="157" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A157" t="str">
         <x:v>global_cycle_month.xlsx</x:v>
       </x:c>
@@ -3392,10 +3392,10 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F157" s="1" t="str">
-        <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同数值，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="158">
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型DOUBLE；在线浮点型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A158" t="str">
         <x:v>global_cycle_month.xlsx</x:v>
       </x:c>
@@ -3412,10 +3412,10 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F158" s="1" t="str">
-        <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同数值，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="159">
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型DOUBLE；在线浮点型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A159" t="str">
         <x:v>global_cycle_month.xlsx</x:v>
       </x:c>
@@ -3432,7 +3432,7 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F159" s="1" t="str">
-        <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同数值，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型DOUBLE；在线浮点型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
       </x:c>
     </x:row>
     <x:row r="160">
@@ -3455,7 +3455,7 @@
         <x:v>P0经验：平台可能误判integer,须确认double/浮点；XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；整数类型一致；合同来源：数据字典_V4.1.xlsx</x:v>
       </x:c>
     </x:row>
-    <x:row r="161">
+    <x:row r="161" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A161" t="str">
         <x:v>global_cycle_month.xlsx</x:v>
       </x:c>
@@ -3472,10 +3472,10 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F161" s="1" t="str">
-        <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同数值，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="162">
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型DOUBLE；在线浮点型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A162" t="str">
         <x:v>global_cycle_month.xlsx</x:v>
       </x:c>
@@ -3492,10 +3492,10 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F162" s="1" t="str">
-        <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同数值，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="163">
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型DOUBLE；在线浮点型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A163" t="str">
         <x:v>global_cycle_month.xlsx</x:v>
       </x:c>
@@ -3512,10 +3512,10 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F163" s="1" t="str">
-        <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同数值，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="164">
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型DOUBLE；在线浮点型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A164" t="str">
         <x:v>global_cycle_month.xlsx</x:v>
       </x:c>
@@ -3532,10 +3532,10 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F164" s="1" t="str">
-        <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同数值，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="165">
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型DOUBLE；在线浮点型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A165" t="str">
         <x:v>global_cycle_month.xlsx</x:v>
       </x:c>
@@ -3552,10 +3552,10 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F165" s="1" t="str">
-        <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同数值，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="166">
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型DOUBLE；在线浮点型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A166" t="str">
         <x:v>global_cycle_month.xlsx</x:v>
       </x:c>
@@ -3572,10 +3572,10 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F166" s="1" t="str">
-        <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同数值，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="167">
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型DOUBLE；在线浮点型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A167" t="str">
         <x:v>global_cycle_month.xlsx</x:v>
       </x:c>
@@ -3592,10 +3592,10 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F167" s="1" t="str">
-        <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同数值，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="168">
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型DOUBLE；在线浮点型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A168" t="str">
         <x:v>global_cycle_month.xlsx</x:v>
       </x:c>
@@ -3612,10 +3612,10 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F168" s="1" t="str">
-        <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同数值，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="169">
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型DOUBLE；在线浮点型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A169" t="str">
         <x:v>global_cycle_month.xlsx</x:v>
       </x:c>
@@ -3632,10 +3632,10 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F169" s="1" t="str">
-        <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同数值，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="170">
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型DOUBLE；在线浮点型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A170" t="str">
         <x:v>global_cycle_month.xlsx</x:v>
       </x:c>
@@ -3652,10 +3652,10 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F170" s="1" t="str">
-        <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同数值，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="171">
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型DOUBLE；在线浮点型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A171" t="str">
         <x:v>global_cycle_month.xlsx</x:v>
       </x:c>
@@ -3672,7 +3672,7 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F171" s="1" t="str">
-        <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同数值，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型DOUBLE；在线浮点型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
       </x:c>
     </x:row>
     <x:row r="172">
@@ -3875,7 +3875,7 @@
         <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；文本类型一致；合同来源：数据字典_V4.1.xlsx</x:v>
       </x:c>
     </x:row>
-    <x:row r="182">
+    <x:row r="182" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A182" t="str">
         <x:v>global_cycle_month.xlsx</x:v>
       </x:c>
@@ -3892,7 +3892,7 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F182" s="1" t="str">
-        <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同日期，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型DATE；在线日期一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
       </x:c>
     </x:row>
     <x:row r="183">
@@ -4695,7 +4695,7 @@
         <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；文本类型一致；合同来源：数据字典_V4.1.xlsx</x:v>
       </x:c>
     </x:row>
-    <x:row r="223">
+    <x:row r="223" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A223" t="str">
         <x:v>company_overseas_exposure.xlsx</x:v>
       </x:c>
@@ -4712,10 +4712,10 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F223" s="1" t="str">
-        <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同整数，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="224">
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型INTEGER；在线整型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="224" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A224" t="str">
         <x:v>company_overseas_exposure.xlsx</x:v>
       </x:c>
@@ -4732,7 +4732,7 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F224" s="1" t="str">
-        <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同日期，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型DATE；在线日期一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
       </x:c>
     </x:row>
     <x:row r="225">
@@ -4995,7 +4995,7 @@
         <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；数值类型一致；合同来源：数据字典_V4.1.xlsx</x:v>
       </x:c>
     </x:row>
-    <x:row r="238">
+    <x:row r="238" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A238" t="str">
         <x:v>company_overseas_exposure.xlsx</x:v>
       </x:c>
@@ -5012,10 +5012,10 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F238" s="1" t="str">
-        <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同数值，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="239">
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型DOUBLE；在线浮点型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="239" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A239" t="str">
         <x:v>company_overseas_exposure.xlsx</x:v>
       </x:c>
@@ -5032,10 +5032,10 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F239" s="1" t="str">
-        <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同数值，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="240">
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型DOUBLE；在线浮点型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="240" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A240" t="str">
         <x:v>company_overseas_exposure.xlsx</x:v>
       </x:c>
@@ -5052,7 +5052,7 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F240" s="1" t="str">
-        <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同数值，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型DOUBLE；在线浮点型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
       </x:c>
     </x:row>
     <x:row r="241">
@@ -5095,7 +5095,7 @@
         <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；源端全空，平台字符串仅作占位类型记录；缺失保持空，不填0</x:v>
       </x:c>
     </x:row>
-    <x:row r="243">
+    <x:row r="243" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A243" t="str">
         <x:v>company_overseas_exposure.xlsx</x:v>
       </x:c>
@@ -5112,7 +5112,7 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F243" s="1" t="str">
-        <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同数值，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型DOUBLE；在线浮点型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
       </x:c>
     </x:row>
     <x:row r="244">
@@ -5215,7 +5215,7 @@
         <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；源端全空，平台字符串仅作占位类型记录；缺失保持空，不填0</x:v>
       </x:c>
     </x:row>
-    <x:row r="249">
+    <x:row r="249" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A249" t="str">
         <x:v>company_overseas_exposure.xlsx</x:v>
       </x:c>
@@ -5232,7 +5232,7 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F249" s="1" t="str">
-        <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同数值，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型DOUBLE；在线浮点型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
       </x:c>
     </x:row>
     <x:row r="250">
@@ -5455,7 +5455,7 @@
         <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；文本类型一致；合同来源：数据字典_V4.1.xlsx</x:v>
       </x:c>
     </x:row>
-    <x:row r="261">
+    <x:row r="261" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A261" t="str">
         <x:v>bridge_company_geography.xlsx</x:v>
       </x:c>
@@ -5472,7 +5472,7 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F261" s="1" t="str">
-        <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同整数，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型INTEGER；在线整型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
       </x:c>
     </x:row>
     <x:row r="262">
@@ -5995,7 +5995,7 @@
         <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；数值类型一致；合同来源：数据字典_V4.1.xlsx</x:v>
       </x:c>
     </x:row>
-    <x:row r="288">
+    <x:row r="288" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A288" t="str">
         <x:v>portfolio_scenario.xlsx</x:v>
       </x:c>
@@ -6012,7 +6012,7 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F288" s="1" t="str">
-        <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同数值，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型DOUBLE；在线浮点型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
       </x:c>
     </x:row>
     <x:row r="289">
@@ -6295,7 +6295,7 @@
         <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；源端全空，平台字符串仅作占位类型记录；缺失保持空，不填0</x:v>
       </x:c>
     </x:row>
-    <x:row r="303">
+    <x:row r="303" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A303" t="str">
         <x:v>case_evidence.xlsx</x:v>
       </x:c>
@@ -6312,10 +6312,10 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F303" s="1" t="str">
-        <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同日期，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="304">
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型DATE；在线日期一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="304" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A304" t="str">
         <x:v>case_evidence.xlsx</x:v>
       </x:c>
@@ -6332,7 +6332,7 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F304" s="1" t="str">
-        <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同日期，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型DATE；在线日期一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
       </x:c>
     </x:row>
     <x:row r="305">
@@ -7055,7 +7055,7 @@
         <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；文本类型一致；合同来源：数据字典_V4.1.xlsx</x:v>
       </x:c>
     </x:row>
-    <x:row r="341">
+    <x:row r="341" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A341" t="str">
         <x:v>source_registry.xlsx</x:v>
       </x:c>
@@ -7072,10 +7072,10 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F341" s="1" t="str">
-        <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同数值，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="342">
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型DOUBLE；在线浮点型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="342" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A342" t="str">
         <x:v>source_registry.xlsx</x:v>
       </x:c>
@@ -7092,10 +7092,10 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F342" s="1" t="str">
-        <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同数值，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="343">
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型DOUBLE；在线浮点型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="343" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A343" t="str">
         <x:v>source_registry.xlsx</x:v>
       </x:c>
@@ -7112,7 +7112,7 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F343" s="1" t="str">
-        <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同日期，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型DATE；在线日期一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
       </x:c>
     </x:row>
     <x:row r="344">
@@ -7195,7 +7195,7 @@
         <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；文本类型一致；合同来源：数据字典_V4.1.xlsx</x:v>
       </x:c>
     </x:row>
-    <x:row r="348">
+    <x:row r="348" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A348" t="str">
         <x:v>source_registry.xlsx</x:v>
       </x:c>
@@ -7212,7 +7212,7 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F348" s="1" t="str">
-        <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同数值，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型DOUBLE；在线浮点型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
       </x:c>
     </x:row>
     <x:row r="349">
@@ -7255,7 +7255,7 @@
         <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；文本类型一致；合同来源：数据字典_V4.1.xlsx</x:v>
       </x:c>
     </x:row>
-    <x:row r="351">
+    <x:row r="351" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A351" t="str">
         <x:v>source_registry.xlsx</x:v>
       </x:c>
@@ -7272,7 +7272,7 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F351" s="1" t="str">
-        <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同日期，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型DATE；在线日期一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
       </x:c>
     </x:row>
     <x:row r="352">
@@ -7735,7 +7735,7 @@
         <x:v>辅助表(A01生成)；XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；数值类型一致；合同来源：MVP_FIELD_DICTIONARY_V50.xlsx</x:v>
       </x:c>
     </x:row>
-    <x:row r="375">
+    <x:row r="375" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A375" t="str">
         <x:v>MVP_country_latest.xlsx</x:v>
       </x:c>
@@ -7752,7 +7752,7 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F375" s="1" t="str">
-        <x:v>辅助表(A01生成)；XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同日期，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型DATE；在线日期一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
       </x:c>
     </x:row>
     <x:row r="376">
@@ -7775,7 +7775,7 @@
         <x:v>辅助表(A01生成)；XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；数值类型一致；合同来源：MVP_FIELD_DICTIONARY_V50.xlsx</x:v>
       </x:c>
     </x:row>
-    <x:row r="377">
+    <x:row r="377" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A377" t="str">
         <x:v>MVP_country_latest.xlsx</x:v>
       </x:c>
@@ -7792,10 +7792,10 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F377" s="1" t="str">
-        <x:v>辅助表(A01生成)；XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同日期，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="378">
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型DATE；在线日期一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="378" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A378" t="str">
         <x:v>MVP_country_latest.xlsx</x:v>
       </x:c>
@@ -7812,10 +7812,10 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F378" s="1" t="str">
-        <x:v>辅助表(A01生成)；XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同数值，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="379">
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型DOUBLE；在线浮点型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="379" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A379" t="str">
         <x:v>MVP_country_latest.xlsx</x:v>
       </x:c>
@@ -7832,7 +7832,7 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F379" s="1" t="str">
-        <x:v>辅助表(A01生成)；XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同日期，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型DATE；在线日期一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
       </x:c>
     </x:row>
     <x:row r="380">
@@ -7855,7 +7855,7 @@
         <x:v>辅助表(A01生成)；XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；数值类型一致；合同来源：MVP_FIELD_DICTIONARY_V50.xlsx</x:v>
       </x:c>
     </x:row>
-    <x:row r="381">
+    <x:row r="381" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A381" t="str">
         <x:v>MVP_country_latest.xlsx</x:v>
       </x:c>
@@ -7872,10 +7872,10 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F381" s="1" t="str">
-        <x:v>辅助表(A01生成)；XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同日期，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="382">
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型DATE；在线日期一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="382" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A382" t="str">
         <x:v>MVP_country_latest.xlsx</x:v>
       </x:c>
@@ -7892,7 +7892,7 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F382" s="1" t="str">
-        <x:v>辅助表(A01生成)；XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同数值，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型DOUBLE；在线浮点型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
       </x:c>
     </x:row>
     <x:row r="383">
@@ -7915,7 +7915,7 @@
         <x:v>辅助表(A01生成)；XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；数值类型一致；合同来源：MVP_FIELD_DICTIONARY_V50.xlsx</x:v>
       </x:c>
     </x:row>
-    <x:row r="384">
+    <x:row r="384" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A384" t="str">
         <x:v>MVP_country_latest.xlsx</x:v>
       </x:c>
@@ -7932,7 +7932,7 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F384" s="1" t="str">
-        <x:v>辅助表(A01生成)；XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同数值，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型DOUBLE；在线浮点型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
       </x:c>
     </x:row>
     <x:row r="385">
@@ -8015,7 +8015,7 @@
         <x:v>辅助表(A01生成)；XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；整数类型一致；合同来源：MVP_FIELD_DICTIONARY_V50.xlsx</x:v>
       </x:c>
     </x:row>
-    <x:row r="389">
+    <x:row r="389" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A389" t="str">
         <x:v>MVP_country_latest.xlsx</x:v>
       </x:c>
@@ -8032,10 +8032,10 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F389" s="1" t="str">
-        <x:v>辅助表(A01生成)；XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同数值，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="390">
+        <x:v>2026-09-04分层复核：9/1底表DOUBLE，模型DOUBLE；在线浮点型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="390" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A390" t="str">
         <x:v>MVP_country_latest.xlsx</x:v>
       </x:c>
@@ -8052,7 +8052,7 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F390" s="1" t="str">
-        <x:v>辅助表(A01生成)；XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同整数，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
+        <x:v>2026-09-04分层复核：9/1底表INTEGER，模型INTEGER；在线整型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
       </x:c>
     </x:row>
     <x:row r="391">
@@ -8575,7 +8575,7 @@
         <x:v>辅助表(A01生成)；XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；日期类型一致；合同来源：MVP_FIELD_DICTIONARY_V50.xlsx</x:v>
       </x:c>
     </x:row>
-    <x:row r="417">
+    <x:row r="417" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A417" t="str">
         <x:v>MVP_cycle_state.xlsx</x:v>
       </x:c>
@@ -8592,10 +8592,10 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F417" s="1" t="str">
-        <x:v>辅助表(A01生成)；XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同数值，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="418">
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型DOUBLE；在线浮点型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="418" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A418" t="str">
         <x:v>MVP_cycle_state.xlsx</x:v>
       </x:c>
@@ -8612,10 +8612,10 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F418" s="1" t="str">
-        <x:v>辅助表(A01生成)；XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同数值，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="419">
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型DOUBLE；在线浮点型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="419" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A419" t="str">
         <x:v>MVP_cycle_state.xlsx</x:v>
       </x:c>
@@ -8632,10 +8632,10 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F419" s="1" t="str">
-        <x:v>辅助表(A01生成)；XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同数值，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="420">
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型DOUBLE；在线浮点型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="420" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A420" t="str">
         <x:v>MVP_cycle_state.xlsx</x:v>
       </x:c>
@@ -8652,10 +8652,10 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F420" s="1" t="str">
-        <x:v>辅助表(A01生成)；XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同数值，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="421">
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型DOUBLE；在线浮点型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="421" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A421" t="str">
         <x:v>MVP_cycle_state.xlsx</x:v>
       </x:c>
@@ -8672,7 +8672,7 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F421" s="1" t="str">
-        <x:v>辅助表(A01生成)；XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同数值，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型DOUBLE；在线浮点型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
       </x:c>
     </x:row>
     <x:row r="422">
@@ -8695,7 +8695,7 @@
         <x:v>辅助表(A01生成)；XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；数值类型一致；合同来源：MVP_FIELD_DICTIONARY_V50.xlsx</x:v>
       </x:c>
     </x:row>
-    <x:row r="423">
+    <x:row r="423" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A423" t="str">
         <x:v>MVP_cycle_state.xlsx</x:v>
       </x:c>
@@ -8712,10 +8712,10 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F423" s="1" t="str">
-        <x:v>辅助表(A01生成)；XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同数值，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="424">
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型DOUBLE；在线浮点型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="424" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A424" t="str">
         <x:v>MVP_cycle_state.xlsx</x:v>
       </x:c>
@@ -8732,10 +8732,10 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F424" s="1" t="str">
-        <x:v>辅助表(A01生成)；XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同数值，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="425">
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型DOUBLE；在线浮点型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="425" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A425" t="str">
         <x:v>MVP_cycle_state.xlsx</x:v>
       </x:c>
@@ -8752,7 +8752,7 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F425" s="1" t="str">
-        <x:v>辅助表(A01生成)；XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同数值，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型DOUBLE；在线浮点型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
       </x:c>
     </x:row>
     <x:row r="426">
@@ -8775,7 +8775,7 @@
         <x:v>辅助表(A01生成)；XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；三态1/0/空以可空整数承载；合同来源：MVP_FIELD_DICTIONARY_V50.xlsx</x:v>
       </x:c>
     </x:row>
-    <x:row r="427">
+    <x:row r="427" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A427" t="str">
         <x:v>MVP_cycle_state.xlsx</x:v>
       </x:c>
@@ -8792,10 +8792,10 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F427" s="1" t="str">
-        <x:v>辅助表(A01生成)；XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同三态1/0/空，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="428">
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型INTEGER；在线整型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="428" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A428" t="str">
         <x:v>MVP_cycle_state.xlsx</x:v>
       </x:c>
@@ -8812,10 +8812,10 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F428" s="1" t="str">
-        <x:v>辅助表(A01生成)；XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同三态1/0/空，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="429">
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型INTEGER；在线整型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="429" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A429" t="str">
         <x:v>MVP_cycle_state.xlsx</x:v>
       </x:c>
@@ -8832,10 +8832,10 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F429" s="1" t="str">
-        <x:v>辅助表(A01生成)；XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同三态1/0/空，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="430">
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型INTEGER；在线整型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="430" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A430" t="str">
         <x:v>MVP_cycle_state.xlsx</x:v>
       </x:c>
@@ -8852,10 +8852,10 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F430" s="1" t="str">
-        <x:v>辅助表(A01生成)；XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同三态1/0/空，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="431">
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型INTEGER；在线整型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="431" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A431" t="str">
         <x:v>MVP_cycle_state.xlsx</x:v>
       </x:c>
@@ -8872,10 +8872,10 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F431" s="1" t="str">
-        <x:v>辅助表(A01生成)；XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同三态1/0/空，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="432">
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型INTEGER；在线整型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="432" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A432" t="str">
         <x:v>MVP_cycle_state.xlsx</x:v>
       </x:c>
@@ -8892,10 +8892,10 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F432" s="1" t="str">
-        <x:v>辅助表(A01生成)；XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同三态1/0/空，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="433">
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型INTEGER；在线整型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="433" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A433" t="str">
         <x:v>MVP_cycle_state.xlsx</x:v>
       </x:c>
@@ -8912,7 +8912,7 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F433" s="1" t="str">
-        <x:v>辅助表(A01生成)；XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同三态1/0/空，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型INTEGER；在线整型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
       </x:c>
     </x:row>
     <x:row r="434">
@@ -8975,7 +8975,7 @@
         <x:v>辅助表(A01生成)；XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；文本类型一致；合同来源：MVP_FIELD_DICTIONARY_V50.xlsx</x:v>
       </x:c>
     </x:row>
-    <x:row r="437">
+    <x:row r="437" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A437" t="str">
         <x:v>MVP_cycle_state.xlsx</x:v>
       </x:c>
@@ -8992,7 +8992,7 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F437" s="1" t="str">
-        <x:v>辅助表(A01生成)；XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；类型偏差：合同三态1/0/空，平台STRING；须由A在Smartbi人工改型并重新导出复核</x:v>
+        <x:v>2026-09-04分层复核：9/1底表STRING，模型INTEGER；在线整型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
       </x:c>
     </x:row>
     <x:row r="438">

--- a/V5.0_双人执行工作区/A_数据平台/03_Smartbi证据/A03/SMARTBI_TYPE_AUDIT_V50.xlsx
+++ b/V5.0_双人执行工作区/A_数据平台/03_Smartbi证据/A03/SMARTBI_TYPE_AUDIT_V50.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="类型审计" sheetId="1" r:id="R7f0782d12e9d400a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="类型审计" sheetId="1" r:id="R2e49fbed584a44a6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1995,7 +1995,7 @@
         <x:v>XML证据：XML元数据/A03_METADATA_EXPORT_V50_20260825.xml；数值类型一致；合同来源：数据字典_V4.1.xlsx</x:v>
       </x:c>
     </x:row>
-    <x:row r="88" ht="52.79999923706055" hidden="0" customHeight="1">
+    <x:row r="88" ht="66" hidden="0" customHeight="1">
       <x:c r="A88" t="str">
         <x:v>country_monthly_risk.xlsx</x:v>
       </x:c>
@@ -2012,7 +2012,7 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="F88" s="1" t="str">
-        <x:v>2026-09-04分层复核：9/1底表STRING，模型BIGDECIMAL；在线长浮点型一致。旧FAIL保留底表口径，计算/取值域和B复核待完成。证据：A03_TYPE_PERSISTENCE_20260904/TYPE_LAYER_RECONCILIATION.json。</x:v>
+        <x:v>2026-09-04实测：AVG 375.80匹配源表；MAX 993.56≠47,954.24。底表MAX按文本取值，CAST数值后为47,954.24。模型BIGDECIMAL持久化不等于聚合正确。保留FAIL，待底层修复与B复核。证据：A03_CPI_RUNTIME_RECHECK_20260904/README.md。</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
